--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486805_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486805_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.91</v>
+        <v>8.103300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8215</v>
+        <v>4.8907</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0885</v>
+        <v>3.2126</v>
       </c>
       <c r="G2" t="n">
         <v>6.7863</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.1586</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3234</v>
+        <v>0.3926</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3582</v>
+        <v>-0.234</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.166</v>
+        <v>5.1915</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9863</v>
+        <v>1.8328</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1797</v>
+        <v>3.3587</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9587</v>
+        <v>3.363</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6143</v>
+        <v>2.6758</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3443</v>
+        <v>0.6872</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3943</v>
+        <v>2.178</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4772</v>
+        <v>2.0559</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9171</v>
+        <v>0.1221</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5643</v>
+        <v>1.1849</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1371</v>
+        <v>0.6198</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4272</v>
+        <v>0.5651</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3862</v>
+        <v>2.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8962</v>
+        <v>-0.1931</v>
       </c>
       <c r="R3" t="n">
-        <v>2.51</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0223</v>
+        <v>-0.1103</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.1521</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1054</v>
+        <v>0.0419</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5712</v>
+        <v>-0.5712</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0591</v>
+        <v>4.7646</v>
       </c>
       <c r="E4" t="n">
-        <v>1.626</v>
+        <v>1.8829</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4332</v>
+        <v>2.8817</v>
       </c>
       <c r="G4" t="n">
-        <v>3.363</v>
+        <v>4.9587</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6758</v>
+        <v>2.6143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6872</v>
+        <v>2.3443</v>
       </c>
       <c r="J4" t="n">
-        <v>2.178</v>
+        <v>4.3943</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0559</v>
+        <v>2.4772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1221</v>
+        <v>1.9171</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1849</v>
+        <v>0.5643</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6198</v>
+        <v>0.1371</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5651</v>
+        <v>0.4272</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2.8962</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.51</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.1931</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.7031</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.2426</v>
+        <v>-0.3791</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.359</v>
+        <v>-0.1865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1164</v>
+        <v>-0.1926</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5712</v>
+        <v>0.5712</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2606</v>
+        <v>1.7198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2931</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9675</v>
+        <v>1.1165</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2043</v>
@@ -844,13 +844,13 @@
         <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9212</v>
+        <v>-0.462</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3036</v>
+        <v>0.0067</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6177</v>
+        <v>-0.4687</v>
       </c>
       <c r="V5" t="n">
         <v>1.2277</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>G. CAMPOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.893</v>
+        <v>0.973</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2524</v>
+        <v>2.339</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1454</v>
+        <v>-1.366</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9288</v>
+        <v>0.8767</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3726</v>
+        <v>-0.1587</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5562</v>
+        <v>1.0354</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.197</v>
+        <v>3.5391</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4412</v>
+        <v>1.0139</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2442</v>
+        <v>2.5252</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7318</v>
+        <v>-2.6625</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06859999999999999</v>
+        <v>-1.1727</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8003</v>
+        <v>-1.4898</v>
       </c>
       <c r="P6" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.3515</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.3862</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.7377</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.7558</v>
+        <v>-0.0968</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3307</v>
+        <v>-0.0417</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4251</v>
+        <v>-0.0551</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6011</v>
+        <v>0.7376</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3647</v>
+        <v>-0.0544</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9658</v>
+        <v>0.792</v>
       </c>
       <c r="G7" t="n">
         <v>0.0137</v>
@@ -1000,13 +1000,13 @@
         <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0774</v>
+        <v>0.2139</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5795</v>
+        <v>-0.2692</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6569</v>
+        <v>0.4831</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2277</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5248</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0883</v>
+        <v>-0.3559</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6131</v>
+        <v>0.9964</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2572</v>
+        <v>-0.9288</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2414</v>
+        <v>-0.3726</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0158</v>
+        <v>-0.5562</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0701</v>
+        <v>-0.197</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7234</v>
+        <v>-0.4412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6534</v>
+        <v>0.2442</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1871</v>
+        <v>-0.7318</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4821</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6692</v>
+        <v>-0.8003</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6895</v>
+        <v>0.5034</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6616</v>
+        <v>0.2273</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0279</v>
+        <v>0.2761</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRÍGUEZ</t>
+          <t>J. RIVERA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3028</v>
+        <v>-0.006</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7185</v>
+        <v>2.0801</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4157</v>
+        <v>-2.0861</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8767</v>
+        <v>1.4521</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1587</v>
+        <v>0.1997</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0354</v>
+        <v>1.2524</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5391</v>
+        <v>2.6664</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0139</v>
+        <v>0.0621</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5252</v>
+        <v>2.6043</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6625</v>
+        <v>-1.2143</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1727</v>
+        <v>0.1376</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4898</v>
+        <v>-1.3519</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1931</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.1931</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.1585</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3515</v>
-      </c>
       <c r="S9" t="n">
-        <v>-0.767</v>
+        <v>-0.5586</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6622</v>
+        <v>-0.3932</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1048</v>
+        <v>-0.1654</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RIVERA RODRÍGUEZ</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2584</v>
+        <v>-0.1991</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9767</v>
+        <v>-0.8122</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.235</v>
+        <v>0.6131</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4521</v>
+        <v>-0.2572</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1997</v>
+        <v>-0.2414</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2524</v>
+        <v>-0.0158</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6664</v>
+        <v>-0.0701</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0621</v>
+        <v>-0.7234</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6043</v>
+        <v>0.6534</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2143</v>
+        <v>-0.1871</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1376</v>
+        <v>0.4821</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3519</v>
+        <v>-0.6692</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.0345</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4966</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3144</v>
+        <v>0.0279</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8995</v>
+        <v>0.2856</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4902</v>
+        <v>-1.0599</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3418</v>
+        <v>-1.135</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1484</v>
+        <v>0.0751</v>
       </c>
       <c r="G11" t="n">
         <v>1.2711</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5683</v>
+        <v>-0.1379</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4691</v>
+        <v>-0.2623</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.1243</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9768</v>
+        <v>-2.1092</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2784</v>
+        <v>-0.4853</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6984</v>
+        <v>-1.6239</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4785</v>
@@ -1390,13 +1390,13 @@
         <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4357</v>
+        <v>0.3034</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5239</v>
+        <v>0.3171</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5133</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4746</v>
+        <v>-3.2389</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3967</v>
+        <v>-2.0864</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0779</v>
+        <v>-1.1524</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1277</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6012</v>
+        <v>-0.3655</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7174</v>
+        <v>-0.4071</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1161</v>
+        <v>0.0416</v>
       </c>
       <c r="V13" t="n">
         <v>0.5712</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.5174</v>
+        <v>15.5173</v>
       </c>
       <c r="E14" t="n">
-        <v>8.6998</v>
+        <v>8.699599999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>6.817800000000002</v>
+        <v>6.817699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>14.7251</v>
       </c>
       <c r="H14" t="n">
-        <v>8.621300000000002</v>
+        <v>8.621299999999998</v>
       </c>
       <c r="I14" t="n">
         <v>6.103800000000001</v>
@@ -1522,16 +1522,16 @@
         <v>21.3555</v>
       </c>
       <c r="K14" t="n">
-        <v>8.627500000000001</v>
+        <v>8.6275</v>
       </c>
       <c r="L14" t="n">
         <v>12.7282</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.6305</v>
+        <v>-6.630500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.006300000000000028</v>
+        <v>-0.006300000000000083</v>
       </c>
       <c r="O14" t="n">
         <v>-6.6242</v>
@@ -1549,7 +1549,7 @@
         <v>-0.9654</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8309000000000001</v>
+        <v>-0.8308</v>
       </c>
       <c r="U14" t="n">
         <v>-0.1346000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0603</v>
+        <v>4.8795</v>
       </c>
       <c r="E15" t="n">
-        <v>2.122</v>
+        <v>2.7425</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9383</v>
+        <v>2.137</v>
       </c>
       <c r="G15" t="n">
         <v>4.718</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7502</v>
+        <v>0.0689</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.745</v>
+        <v>-0.1245</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0052</v>
+        <v>0.1934</v>
       </c>
       <c r="V15" t="n">
         <v>0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7768</v>
+        <v>3.2361</v>
       </c>
       <c r="E16" t="n">
-        <v>3.348</v>
+        <v>3.6582</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.4221</v>
       </c>
       <c r="G16" t="n">
         <v>0.8815</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4248</v>
+        <v>0.0344</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3866</v>
+        <v>-0.0764</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0382</v>
+        <v>0.1108</v>
       </c>
       <c r="V16" t="n">
         <v>2.1271</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1108</v>
+        <v>0.9744</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2814</v>
+        <v>-0.0288</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8294</v>
+        <v>1.0032</v>
       </c>
       <c r="G17" t="n">
         <v>0.9496</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1324</v>
+        <v>-0.2688</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0273</v>
+        <v>-0.283</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1597</v>
+        <v>0.0142</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1106</v>
+        <v>0.5616</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6312</v>
+        <v>3.2175</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5207</v>
+        <v>-2.6559</v>
       </c>
       <c r="G18" t="n">
         <v>-0.455</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7007</v>
+        <v>0.1518</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1928</v>
+        <v>-0.2208</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5079</v>
+        <v>0.3726</v>
       </c>
       <c r="V18" t="n">
         <v>0.2856</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>J. BAEZ CARRERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.857</v>
+        <v>-1.0774</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0024</v>
+        <v>0.1021</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1454</v>
+        <v>-1.1794</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6096</v>
+        <v>-1.0498</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9721</v>
+        <v>0.0896</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6375</v>
+        <v>-1.1394</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1879</v>
+        <v>0.1021</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3507</v>
+        <v>0.0207</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1628</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4217</v>
+        <v>-1.1519</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6214</v>
+        <v>0.0689</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8003</v>
+        <v>-1.2208</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1734</v>
+        <v>-0.0275</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1509</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0225</v>
+        <v>-0.0275</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BAEZ CARRERAS</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.978</v>
+        <v>-1.8174</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1021</v>
+        <v>0.4901</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0801</v>
+        <v>-2.3076</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0498</v>
+        <v>-3.3453</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0896</v>
+        <v>-1.3039</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1394</v>
+        <v>-2.0414</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1021</v>
+        <v>1.1456</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0207</v>
+        <v>0.49</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1519</v>
+        <v>-4.4909</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0689</v>
+        <v>-1.7939</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2208</v>
+        <v>-2.697</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0718</v>
+        <v>0.655</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.3099</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0718</v>
+        <v>0.3451</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1414</v>
+        <v>-2.2719</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1799</v>
+        <v>-2.2435</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3213</v>
+        <v>-0.0284</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3453</v>
+        <v>-3.6096</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3039</v>
+        <v>-2.9721</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0414</v>
+        <v>-0.6375</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1456</v>
+        <v>-2.1879</v>
       </c>
       <c r="K21" t="n">
-        <v>0.49</v>
+        <v>-2.3507</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.1628</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.4909</v>
+        <v>-1.4217</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7939</v>
+        <v>-0.6214</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.697</v>
+        <v>-0.8003</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>0.331</v>
+        <v>0.7585</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0004</v>
+        <v>0.9099</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3314</v>
+        <v>-0.1513</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.235</v>
+        <v>-4.8365</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8354</v>
+        <v>-3.5251</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3996</v>
+        <v>-1.3114</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3199</v>
@@ -2170,13 +2170,13 @@
         <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4743</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5795</v>
+        <v>-0.2692</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1051</v>
+        <v>0.1934</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4711</v>
+        <v>-5.1635</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2669</v>
+        <v>-4.3703</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2042</v>
+        <v>-0.7931</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7231</v>
@@ -2248,13 +2248,13 @@
         <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4025</v>
+        <v>0.7101</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6339</v>
+        <v>0.5305</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2315</v>
+        <v>0.1796</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5712</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.8934</v>
+        <v>-9.312900000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.3776</v>
+        <v>-6.8605</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5158</v>
+        <v>-2.4524</v>
       </c>
       <c r="G24" t="n">
         <v>-7.7714</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9322</v>
+        <v>-0.3517</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1588</v>
+        <v>-0.6417</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2266</v>
+        <v>0.29</v>
       </c>
       <c r="V24" t="n">
         <v>1.5133</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.5174</v>
+        <v>-14.828</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.817699999999999</v>
+        <v>-6.817799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.6997</v>
+        <v>-8.0101</v>
       </c>
       <c r="G25" t="n">
         <v>-14.725</v>
@@ -2374,13 +2374,13 @@
         <v>-8.6212</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.1038</v>
+        <v>-6.103799999999998</v>
       </c>
       <c r="J25" t="n">
         <v>6.630299999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.006299999999999972</v>
+        <v>0.006299999999999084</v>
       </c>
       <c r="L25" t="n">
         <v>6.624299999999999</v>
@@ -2404,13 +2404,13 @@
         <v>14.4807</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9655000000000001</v>
+        <v>1.6549</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1346000000000001</v>
+        <v>0.1347</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8306999999999999</v>
+        <v>1.5203</v>
       </c>
       <c r="V25" t="n">
         <v>3.0692</v>
